--- a/teacher_forms/019_sunday_school_survey--teacher_forms.xlsx
+++ b/teacher_forms/019_sunday_school_survey--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'i_love_it',_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'I love it', 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'i_like_it',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'I like it', 'value': 'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'i_dislike_it',_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'I dislike it', 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'bible',_'value':_'bible'}</t>
+          <t>bible</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Bible', 'value': 'Bible'}</t>
+          <t>Bible</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sunday_school',_'value':_'sunday_school'}</t>
+          <t>sunday_school</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Sunday school', 'value': 'Sunday school'}</t>
+          <t>Sunday school</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent',_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent', 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
